--- a/hourly datasets/cap_gen_year6final.xlsx
+++ b/hourly datasets/cap_gen_year6final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1055014252150202</v>
+        <v>0.1003043894742144</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1223643052292021</v>
+        <v>0.1235778000934808</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2278657304442223</v>
+        <v>0.2238821895676952</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1543637739269478</v>
+        <v>0.1594289355569783</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2598651991419679</v>
+        <v>0.2597333250311928</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1804955279417598</v>
+        <v>0.1885740813114427</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.28599695315678</v>
+        <v>0.2888784707856571</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +549,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1949553919506408</v>
+        <v>0.2023916894234485</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01001588205362942</v>
+        <v>0.00954359854327996</v>
       </c>
       <c r="D6" t="n">
-        <v>19.42857643401977</v>
+        <v>20.44569291769191</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0140652266181283</v>
+        <v>0.01172374469028952</v>
       </c>
       <c r="F6" t="n">
-        <v>0.175252416895114</v>
+        <v>0.1836228419841387</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2146583670061658</v>
+        <v>0.2211605368627587</v>
       </c>
       <c r="H6" t="n">
-        <v>0.300456817165661</v>
+        <v>0.3026960788976629</v>
       </c>
     </row>
     <row r="7">
@@ -577,15 +577,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02133977971314975</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+        <v>0.01580672132583653</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.001140900830245</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.781986061688856</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.008029050719791748</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01356965593573987</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01804378671593321</v>
+      </c>
       <c r="H7" t="n">
-        <v>0.1268412049281699</v>
+        <v>0.116111110800051</v>
       </c>
     </row>
     <row r="8">
@@ -595,15 +605,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01956737982069295</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+        <v>0.01302984892876952</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.001130136691877216</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.215154334793178</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.005502614621277326</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0108114501151457</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01524824774239313</v>
+      </c>
       <c r="H8" t="n">
-        <v>0.1250688050357131</v>
+        <v>0.1133342384029839</v>
       </c>
     </row>
     <row r="9">
@@ -613,25 +633,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01967619388672123</v>
+        <v>0.01030882751605588</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002473789470562971</v>
+        <v>0.0007921874410763432</v>
       </c>
       <c r="D9" t="n">
-        <v>2.231242862100606</v>
+        <v>1.423952018556152</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01607087454981219</v>
+        <v>0.005261429859647774</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01480674496207632</v>
+        <v>0.008755519071589252</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02454564281136651</v>
+        <v>0.01186213596052255</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1251776191017414</v>
+        <v>0.1106132169902703</v>
       </c>
     </row>
     <row r="10">
@@ -641,25 +661,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01819615792027296</v>
+        <v>0.01001408756604583</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001706920798387876</v>
+        <v>0.0006272824080553866</v>
       </c>
       <c r="D10" t="n">
-        <v>2.357010790265366</v>
+        <v>1.588725948074626</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007233561167894183</v>
+        <v>0.002683282531910164</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01484935047587101</v>
+        <v>0.008784322703868808</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02154296536467539</v>
+        <v>0.01124385242822263</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1236975831352931</v>
+        <v>0.1103184770402603</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +689,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0303489923793352</v>
+        <v>0.02935037622368065</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -677,7 +697,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1358504175943554</v>
+        <v>0.1296547656978951</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +707,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04891898940062141</v>
+        <v>0.04841103071812583</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -695,7 +715,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1544204146156416</v>
+        <v>0.1487154201923402</v>
       </c>
     </row>
     <row r="13">
@@ -705,7 +725,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06510632449043699</v>
+        <v>0.0622661507245328</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -713,7 +733,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1706077497054572</v>
+        <v>0.1625705401987472</v>
       </c>
     </row>
     <row r="14">
@@ -723,7 +743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07010579993015824</v>
+        <v>0.06876885179417967</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -731,7 +751,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1756072251451784</v>
+        <v>0.1690732412683941</v>
       </c>
     </row>
     <row r="15">
@@ -741,7 +761,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07370156985864657</v>
+        <v>0.07154600111301303</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -749,7 +769,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1792029950736667</v>
+        <v>0.1718503905872275</v>
       </c>
     </row>
     <row r="16">
@@ -759,7 +779,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07686203111217532</v>
+        <v>0.07497191948954907</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -767,7 +787,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1823634563271955</v>
+        <v>0.1752763089637635</v>
       </c>
     </row>
     <row r="17">
@@ -777,7 +797,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0814021779321821</v>
+        <v>0.07867094244726301</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -785,7 +805,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1869036031472023</v>
+        <v>0.1789753319214774</v>
       </c>
     </row>
     <row r="18">
@@ -795,22 +815,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1055014252150202</v>
+        <v>-0.1003043894742144</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01028323408717581</v>
+        <v>0.00949427955794825</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.0575072969968</v>
+        <v>-16.9706431919026</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03729676889284375</v>
+        <v>0.03592237477351384</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1257324288707526</v>
+        <v>-0.1189566123414763</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08527042155928778</v>
+        <v>-0.08165216660695244</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -823,7 +843,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08375116361469076</v>
+        <v>0.08119046676174217</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -831,7 +851,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1892525888297109</v>
+        <v>0.1814948562359566</v>
       </c>
     </row>
     <row r="20">
@@ -841,25 +861,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08702112339154074</v>
+        <v>0.08447280187875307</v>
       </c>
       <c r="C20" t="n">
-        <v>0.007828776380724812</v>
+        <v>0.007618627438018686</v>
       </c>
       <c r="D20" t="n">
-        <v>1018685867.564496</v>
+        <v>996527373.9534583</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05548274623810262</v>
+        <v>0.05549152511432039</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07163032926453368</v>
+        <v>0.06949486410560543</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1024119175185478</v>
+        <v>0.09945073965190061</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1925225486065609</v>
+        <v>0.1847771913529675</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +889,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09187251963339944</v>
+        <v>0.08835337180329707</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +897,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1973739448484196</v>
+        <v>0.1886577612775115</v>
       </c>
     </row>
     <row r="22">
@@ -887,25 +907,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09512302478531502</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.007559825112236007</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1419454891999.033</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.04498861270255855</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.08026888315052809</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.109977166420102</v>
-      </c>
+        <v>0.09213322723479635</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2006244500003352</v>
+        <v>0.1924376167090108</v>
       </c>
     </row>
     <row r="23">
@@ -915,7 +925,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09897289051688896</v>
+        <v>0.09614518072811622</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -923,7 +933,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2044743157319091</v>
+        <v>0.1964495702023306</v>
       </c>
     </row>
     <row r="24">
@@ -933,7 +943,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09870430536441838</v>
+        <v>0.09603031551975931</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -941,7 +951,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.2042057305794385</v>
+        <v>0.1963347049939737</v>
       </c>
     </row>
     <row r="25">
@@ -951,25 +961,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1043448419642999</v>
+        <v>0.1017904350977646</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007971645305570303</v>
+        <v>0.007446142534109927</v>
       </c>
       <c r="D25" t="n">
-        <v>20.84991429154281</v>
+        <v>20.66993259116041</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05534011883655374</v>
+        <v>0.05109678188701523</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08866328690278645</v>
+        <v>0.08716466089704988</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1200263970258132</v>
+        <v>0.1164162092984791</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2098462671793201</v>
+        <v>0.2020948245719791</v>
       </c>
     </row>
     <row r="26">
@@ -979,25 +989,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1043956610411623</v>
+        <v>0.1030847706133395</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008426823957779054</v>
+        <v>0.007315759808076176</v>
       </c>
       <c r="D26" t="n">
-        <v>1032466629595.513</v>
+        <v>1009623124018.266</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06334589898020578</v>
+        <v>0.05710146424449595</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08775956981154608</v>
+        <v>0.08870937443365391</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1210317522707784</v>
+        <v>0.1174601667930247</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2098970862561825</v>
+        <v>0.2033891600875539</v>
       </c>
     </row>
     <row r="27">
@@ -1007,25 +1017,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.112019832054445</v>
+        <v>0.1104299413007895</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007584406861219519</v>
+        <v>0.007385300177843388</v>
       </c>
       <c r="D27" t="n">
-        <v>22.12649488213892</v>
+        <v>22.15290382716814</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05512387243952326</v>
+        <v>0.05211721250163029</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09712583766759547</v>
+        <v>0.09592654702741678</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1269138264412949</v>
+        <v>0.1249333355741628</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2175212572694651</v>
+        <v>0.2107343307750039</v>
       </c>
     </row>
     <row r="28">
@@ -1035,25 +1045,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1158879859826247</v>
+        <v>0.1153604750746791</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007907565227186959</v>
+        <v>0.007592986484206903</v>
       </c>
       <c r="D28" t="n">
-        <v>22.15229369508844</v>
+        <v>22.28856150240042</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0842547485804046</v>
+        <v>0.08037256710119016</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1003567383376262</v>
+        <v>0.1004545061998153</v>
       </c>
       <c r="G28" t="n">
-        <v>0.131419233627623</v>
+        <v>0.130266443949542</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2213894111976449</v>
+        <v>0.2156648645488935</v>
       </c>
     </row>
     <row r="29">
@@ -1063,25 +1073,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0212273710948751</v>
+        <v>0.007433600120549059</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002800350282614289</v>
+        <v>0.0007060968221940316</v>
       </c>
       <c r="D29" t="n">
-        <v>2.719612804864009</v>
+        <v>1.891244414107075</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01777532955774431</v>
+        <v>0.0148065665555777</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01567169048919264</v>
+        <v>0.006047559713569587</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02678305170055838</v>
+        <v>0.008819640527528431</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1267287963098953</v>
+        <v>0.1077379895947635</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year6final.xlsx
+++ b/hourly datasets/cap_gen_year6final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2173622283811848</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1003043894742144</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0940387000061219</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1235778000934808</v>
+        <v>0.3790437854815675</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2238821895676952</v>
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2557202571065046</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1594289355569783</v>
+        <v>0.3843154023946172</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2597333250311928</v>
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2609918740195543</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1885740813114427</v>
+        <v>0.3801267313814238</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.2888784707856571</v>
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2568032030063609</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +566,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2023916894234485</v>
+        <v>0.3763466316076542</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00954359854327996</v>
+        <v>0.009551245657497332</v>
       </c>
       <c r="D6" t="n">
-        <v>20.44569291769191</v>
+        <v>20.46207568445288</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01172374469028952</v>
+        <v>0.01173313871648366</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1836228419841387</v>
+        <v>0.183769975671626</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2211605368627587</v>
+        <v>0.2213377488313987</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3026960788976629</v>
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2530231032325913</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +597,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01580672132583653</v>
+        <v>0.4929186658623227</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001140900830245</v>
+        <v>0.00280753634473038</v>
       </c>
       <c r="D7" t="n">
-        <v>2.781986061688856</v>
+        <v>26.76417506314903</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008029050719791748</v>
+        <v>0.01067130341422569</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01356965593573987</v>
+        <v>0.05179810877337199</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01804378671593321</v>
+        <v>0.06280666700374407</v>
       </c>
       <c r="H7" t="n">
-        <v>0.116111110800051</v>
+        <v>114</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3695951374872599</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +628,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01302984892876952</v>
+        <v>0.4884389072592</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001130136691877216</v>
+        <v>0.002686425676535808</v>
       </c>
       <c r="D8" t="n">
-        <v>2.215154334793178</v>
+        <v>19.20630347783747</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005502614621277326</v>
+        <v>0.007602578944285381</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0108114501151457</v>
+        <v>0.04171559803652906</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01524824774239313</v>
+        <v>0.05225490324081997</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1133342384029839</v>
+        <v>114</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3651153788841371</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +659,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01030882751605588</v>
+        <v>0.4714034270731759</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0007921874410763432</v>
+        <v>0.002222040428020406</v>
       </c>
       <c r="D9" t="n">
-        <v>1.423952018556152</v>
+        <v>-7.798795885195466</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005261429859647774</v>
+        <v>0.00686380022166549</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008755519071589252</v>
+        <v>0.02196166903198379</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01186213596052255</v>
+        <v>0.03067426769434748</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1106132169902703</v>
+        <v>114</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.348079898698113</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +690,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01001408756604583</v>
+        <v>0.4726719878557138</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0006272824080553866</v>
+        <v>0.002306781766550337</v>
       </c>
       <c r="D10" t="n">
-        <v>1.588725948074626</v>
+        <v>-3.389645188976174</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002683282531910164</v>
+        <v>0.00360966063931309</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008784322703868808</v>
+        <v>0.0219682523047032</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01124385242822263</v>
+        <v>0.03101233386831945</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1103184770402603</v>
+        <v>114</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.349348459480651</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +721,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02935037622368065</v>
+        <v>0.2598867925644448</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +729,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1296547656978951</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1365632641893819</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +742,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04841103071812583</v>
+        <v>0.2841306696428262</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +750,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1487154201923402</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1608071412677633</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +763,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0622661507245328</v>
+        <v>0.300030145675027</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +771,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1625705401987472</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1767066172999641</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +784,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06876885179417967</v>
+        <v>0.3079399764076906</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +792,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1690732412683941</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1846164480326277</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +805,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07154600111301303</v>
+        <v>0.3154785891279858</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +813,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1718503905872275</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1921550607529229</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +826,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07497191948954907</v>
+        <v>0.3201065509233317</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +834,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1752763089637635</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1967830225482688</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +847,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07867094244726301</v>
+        <v>0.3248392070209647</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +855,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1789753319214774</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2015156786459019</v>
       </c>
     </row>
     <row r="18">
@@ -815,24 +868,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1003043894742144</v>
+        <v>0.1233235283750629</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00949427955794825</v>
+        <v>0.009089107761376789</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.9706431919026</v>
+        <v>-16.52477210168849</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03592237477351384</v>
+        <v>0.03579392064954345</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1189566123414763</v>
+        <v>-0.1126400559263071</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08165216660695244</v>
+        <v>-0.07692625314188296</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -843,7 +899,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08119046676174217</v>
+        <v>0.3283648002940828</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +907,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1814948562359566</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2050412719190199</v>
       </c>
     </row>
     <row r="20">
@@ -861,25 +920,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08447280187875307</v>
+        <v>0.3307950847091735</v>
       </c>
       <c r="C20" t="n">
-        <v>0.007618627438018686</v>
+        <v>0.007578978692430018</v>
       </c>
       <c r="D20" t="n">
-        <v>996527373.9534583</v>
+        <v>996521916.5452204</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05549152511432039</v>
+        <v>0.05524011741437584</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06949486410560543</v>
+        <v>0.06939933685115593</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09945073965190061</v>
+        <v>0.09919953054455198</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1847771913529675</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2074715563341106</v>
       </c>
     </row>
     <row r="21">
@@ -889,7 +951,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08835337180329707</v>
+        <v>0.3368895141489883</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -897,7 +959,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1886577612775115</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2135659857739254</v>
       </c>
     </row>
     <row r="22">
@@ -907,7 +972,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09213322723479635</v>
+        <v>0.3397308642018788</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -915,7 +980,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1924376167090108</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2164073358268159</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +993,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09614518072811622</v>
+        <v>0.3474176169707398</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -933,7 +1001,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.1964495702023306</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2240940885956769</v>
       </c>
     </row>
     <row r="24">
@@ -943,7 +1014,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09603031551975931</v>
+        <v>0.3519103721446226</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -951,7 +1022,10 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.1963347049939737</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2285868437695597</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +1035,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1017904350977646</v>
+        <v>0.3588247343119078</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007446142534109927</v>
+        <v>0.007432205350385059</v>
       </c>
       <c r="D25" t="n">
-        <v>20.66993259116041</v>
+        <v>20.61624820192965</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05109678188701523</v>
+        <v>0.05102600185904805</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08716466089704988</v>
+        <v>0.08691571717036914</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1164162092984791</v>
+        <v>0.1161125002467798</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2020948245719791</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2355012059368449</v>
       </c>
     </row>
     <row r="26">
@@ -989,25 +1066,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1030847706133395</v>
+        <v>0.3609074575923708</v>
       </c>
       <c r="C26" t="n">
-        <v>0.007315759808076176</v>
+        <v>0.007299104737612783</v>
       </c>
       <c r="D26" t="n">
-        <v>1009623124018.266</v>
+        <v>1009603710485.426</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05710146424449595</v>
+        <v>0.05701448677716569</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08870937443365391</v>
+        <v>0.08842712591303659</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1174601667930247</v>
+        <v>0.1171124358774211</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2033891600875539</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2375839292173079</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1097,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1104299413007895</v>
+        <v>0.3675660142644406</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007385300177843388</v>
+        <v>0.007350461120091958</v>
       </c>
       <c r="D27" t="n">
-        <v>22.15290382716814</v>
+        <v>22.0202133199111</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05211721250163029</v>
+        <v>0.05200337900384487</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09592654702741678</v>
+        <v>0.09528073721978948</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1249333355741628</v>
+        <v>0.1241505755993623</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2107343307750039</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2442424858893777</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1128,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1153604750746791</v>
+        <v>0.3713780092363089</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007592986484206903</v>
+        <v>0.007541185359797267</v>
       </c>
       <c r="D28" t="n">
-        <v>22.28856150240042</v>
+        <v>22.04245059861521</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08037256710119016</v>
+        <v>0.08018605739555187</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1004545061998153</v>
+        <v>0.09922683480460878</v>
       </c>
       <c r="G28" t="n">
-        <v>0.130266443949542</v>
+        <v>0.1288353106680649</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2156648645488935</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.248054480861246</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1159,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.007433600120549059</v>
+        <v>0.3361478721986009</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0007060968221940316</v>
+        <v>0.001276043253939805</v>
       </c>
       <c r="D29" t="n">
-        <v>1.891244414107075</v>
+        <v>3.328474830673982</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0148065665555777</v>
+        <v>0.224508508377378</v>
       </c>
       <c r="F29" t="n">
-        <v>0.006047559713569587</v>
+        <v>0.00693591899812256</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008819640527528431</v>
+        <v>0.01194373963108918</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1077379895947635</v>
+        <v>61</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.212824343823538</v>
       </c>
     </row>
   </sheetData>
